--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135427023</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135427186</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135427239</v>
       </c>
       <c r="B8" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135426678</v>
       </c>
       <c r="B9" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135427351</v>
       </c>
       <c r="B10" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135426697</v>
       </c>
       <c r="B11" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135426196</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135426435</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135426609</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135426656</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135427063</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135427273</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135427406</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135429477</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135426490</v>
       </c>
       <c r="B20" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135426503</v>
       </c>
       <c r="B21" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>608215</v>
       </c>
       <c r="R27" t="n">
-        <v>6988853</v>
+        <v>6988854</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135426678</v>
       </c>
       <c r="B11" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135426196</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135426435</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135426609</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135426656</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>135427063</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135427273</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135427406</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>135429477</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135426490</v>
       </c>
       <c r="B31" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>135426503</v>
       </c>
       <c r="B33" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>135427033</v>
       </c>
       <c r="B35" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>135425841</v>
       </c>
       <c r="B36" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135426158</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135426518</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135426842</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135429435</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>608215</v>
       </c>
       <c r="R40" t="n">
-        <v>6988854</v>
+        <v>6988853</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4857,7 +4857,7 @@
         <v>135429486</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135742977</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135742987</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135742988</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135742986</v>
       </c>
       <c r="B45" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135429266</v>
       </c>
       <c r="B46" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -4785,7 +4785,7 @@
         <v>608215</v>
       </c>
       <c r="R40" t="n">
-        <v>6988853</v>
+        <v>6988854</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135426678</v>
       </c>
       <c r="B11" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135426196</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135426435</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135426609</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135426656</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>135427063</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135427273</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135427406</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>135429477</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135426490</v>
       </c>
       <c r="B31" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>135426503</v>
       </c>
       <c r="B33" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135426678</v>
       </c>
       <c r="B11" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135426196</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135426435</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135426609</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135426656</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>135427063</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135427273</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135427406</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>135429477</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135426490</v>
       </c>
       <c r="B31" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>135426503</v>
       </c>
       <c r="B33" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>135427033</v>
       </c>
       <c r="B35" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>135425841</v>
       </c>
       <c r="B36" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135426158</v>
       </c>
       <c r="B37" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135426518</v>
       </c>
       <c r="B38" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135426842</v>
       </c>
       <c r="B39" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135429435</v>
       </c>
       <c r="B40" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135429486</v>
       </c>
       <c r="B41" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135742977</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135742987</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135742988</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135742986</v>
       </c>
       <c r="B45" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135429266</v>
       </c>
       <c r="B46" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135426718</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427006</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135427244</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135427023</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135427186</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135427304</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135427239</v>
       </c>
       <c r="B9" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135426678</v>
       </c>
       <c r="B11" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>135426697</v>
       </c>
       <c r="B15" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135426196</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>135426435</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>135426609</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135426656</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>135427063</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>135427273</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>135427406</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>135429477</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>135426490</v>
       </c>
       <c r="B31" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>135426503</v>
       </c>
       <c r="B33" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>135427033</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>135425841</v>
       </c>
       <c r="B36" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>135426158</v>
       </c>
       <c r="B37" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135426518</v>
       </c>
       <c r="B38" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135426842</v>
       </c>
       <c r="B39" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135429435</v>
       </c>
       <c r="B40" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135429486</v>
       </c>
       <c r="B41" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135742977</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135742987</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135742988</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135742986</v>
       </c>
       <c r="B45" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>135429266</v>
       </c>
       <c r="B46" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135742977</v>
       </c>
       <c r="B42" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135742987</v>
       </c>
       <c r="B43" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135742988</v>
       </c>
       <c r="B44" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135742986</v>
       </c>
       <c r="B45" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39195-2025 artfynd.xlsx
+++ b/artfynd/A 39195-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135742978</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135742990</v>
       </c>
       <c r="B10" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>135742989</v>
       </c>
       <c r="B12" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135742991</v>
       </c>
       <c r="B13" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>135742980</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>135742981</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>135742982</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135742992</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>135742976</v>
       </c>
       <c r="B28" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>135742979</v>
       </c>
       <c r="B29" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>135742983</v>
       </c>
       <c r="B30" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>135742984</v>
       </c>
       <c r="B32" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>135742985</v>
       </c>
       <c r="B34" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135742977</v>
       </c>
       <c r="B42" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>135742987</v>
       </c>
       <c r="B43" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135742988</v>
       </c>
       <c r="B44" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>135742986</v>
       </c>
       <c r="B45" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
